--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1515,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1868,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1984,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2002,35 +2034,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2068,7 +2100,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2114,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2139,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,35 +2386,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2447,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2466,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,88 +2491,88 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2550,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2560,65 +2596,61 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2651,12 +2683,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2670,7 +2702,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2706,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2767,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2883,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,7 +2970,3719 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66775D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1255,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1379,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1404,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1440,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1575,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1603,32 +1619,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1636,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1680,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1743,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1752,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1804,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1867,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1868,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,33 +1928,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2100,7 +2140,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2452,7 +2492,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2519,22 +2559,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2572,7 +2612,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2626,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2616,41 +2656,45 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2688,7 +2732,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2746,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2771,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2804,7 +2852,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2866,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2843,7 +2891,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2854,35 +2902,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2963,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2982,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,7 +3007,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2970,35 +3018,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3079,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3098,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3123,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3152,7 +3204,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3218,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3243,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3319,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3338,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3363,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3439,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3458,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,46 +3483,50 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3495,12 +3559,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3578,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3539,18 +3603,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3631,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3573,7 +3641,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3583,40 +3651,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3702,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,17 +3712,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3660,13 +3732,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3755,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3826,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,33 +3836,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3795,22 +3879,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3843,12 +3927,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3946,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3898,7 +3982,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3995,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4005,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3959,12 +4043,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3978,7 +4062,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4098,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4027,32 +4111,32 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4075,12 +4159,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4088,13 +4172,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4230,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4243,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4253,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4291,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4310,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4346,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4359,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4369,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4407,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4426,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4462,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4475,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4423,12 +4523,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4542,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4578,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4591,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4639,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4658,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4694,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4707,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4617,7 +4717,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4655,12 +4755,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4774,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4810,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4823,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4871,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4890,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4926,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4987,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5006,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5031,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5042,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5103,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5122,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5158,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5219,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5238,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5274,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5335,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5354,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5390,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5451,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5470,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5506,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5567,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5586,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5622,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5683,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5702,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5738,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5799,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5818,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5854,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5915,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5934,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5970,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6031,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6050,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6086,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6147,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6166,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6202,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6263,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6282,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6318,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A66775D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6379,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6398,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6434,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6495,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6514,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6550,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6611,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6630,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6666,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6727,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6746,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6671,7 +6771,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6682,7 +6782,3211 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66775D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1753,24 +1753,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2024,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,33 +2052,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2107,32 +2115,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2140,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2164,37 +2176,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2227,32 +2239,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2260,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2284,33 +2300,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2363,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2376,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,33 +2424,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2459,32 +2487,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2492,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2516,37 +2548,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2579,32 +2611,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2612,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2636,17 +2672,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2656,12 +2692,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2732,7 +2768,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2786,7 +2822,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2891,7 +2927,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2968,7 +3004,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3084,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3138,7 +3174,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3258,7 +3294,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3378,7 +3414,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3493,12 +3529,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3600,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,69 +3654,65 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3688,7 +3720,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3702,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3712,99 +3744,95 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3812,7 +3840,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3826,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3836,65 +3864,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3927,12 +3955,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3946,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3971,46 +3999,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4043,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4062,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4087,56 +4119,60 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4164,7 +4200,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4172,29 +4208,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>物理seq32（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4219,46 +4239,50 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4291,12 +4315,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4310,7 +4334,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4335,7 +4359,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4346,7 +4370,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -4359,52 +4383,56 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4412,7 +4440,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4426,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4436,33 +4464,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4507,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4485,7 +4517,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4495,40 +4527,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4542,7 +4578,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4552,33 +4588,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4631,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4601,7 +4641,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4611,40 +4651,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4658,7 +4702,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4668,33 +4712,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4707,60 +4755,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4774,7 +4826,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4784,33 +4836,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4879,32 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq61，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4871,12 +4927,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4884,13 +4940,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4915,7 +4987,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4939,60 +5011,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5006,7 +5082,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5016,33 +5092,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5135,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5065,7 +5145,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5075,40 +5155,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5122,7 +5206,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5132,33 +5216,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5171,22 +5259,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5219,12 +5307,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5238,7 +5326,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5287,60 +5375,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5354,7 +5446,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5364,33 +5456,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5499,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5413,7 +5509,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5451,12 +5547,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5470,7 +5566,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5519,7 +5615,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5529,7 +5625,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5567,12 +5663,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5586,7 +5682,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5635,32 +5731,32 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5683,12 +5779,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5696,13 +5792,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5751,7 +5863,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5761,7 +5873,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5799,12 +5911,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5818,7 +5930,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5867,7 +5979,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5877,7 +5989,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5915,12 +6027,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5934,7 +6046,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5983,7 +6095,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5993,7 +6105,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6003,12 +6115,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6031,12 +6143,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6044,13 +6156,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr"/>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6099,7 +6227,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6109,7 +6237,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6147,12 +6275,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6166,7 +6294,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6215,7 +6343,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6225,7 +6353,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6263,12 +6391,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6282,7 +6410,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6331,22 +6459,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6379,12 +6507,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6398,7 +6526,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6447,22 +6575,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6495,12 +6623,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6514,7 +6642,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,22 +6691,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6611,12 +6739,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6630,7 +6758,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6679,22 +6807,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6727,12 +6855,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6746,7 +6874,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6795,22 +6923,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6843,12 +6971,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6862,7 +6990,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6911,22 +7039,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6964,7 +7092,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6978,7 +7106,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7003,92 +7131,84 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7102,7 +7222,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7112,107 +7232,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7226,7 +7338,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7236,107 +7348,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7350,7 +7454,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7360,107 +7464,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7474,7 +7570,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7484,107 +7580,99 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7598,7 +7686,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7608,17 +7696,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7628,87 +7716,79 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7722,7 +7802,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7732,17 +7812,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7757,40 +7837,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7823,12 +7903,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7842,7 +7922,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7867,46 +7947,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7939,12 +8023,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7958,7 +8042,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7988,41 +8072,45 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8055,12 +8143,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8074,7 +8162,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8099,46 +8187,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8171,12 +8263,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8190,7 +8282,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8226,35 +8318,35 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8287,12 +8379,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8306,7 +8398,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8331,46 +8423,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8403,12 +8499,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8422,7 +8518,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8447,46 +8543,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8519,12 +8619,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8538,7 +8638,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8563,18 +8663,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8691,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A66775D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8597,7 +8701,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8607,40 +8711,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8654,7 +8762,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8664,33 +8772,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8703,52 +8815,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8756,7 +8872,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8770,7 +8886,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8780,33 +8896,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8819,60 +8939,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8886,7 +9010,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8896,33 +9020,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8935,52 +9063,56 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8988,7 +9120,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9002,7 +9134,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9012,17 +9144,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9037,12 +9169,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9187,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9065,7 +9197,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9075,40 +9207,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9122,7 +9258,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9132,33 +9268,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9171,52 +9311,56 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9224,7 +9368,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9238,7 +9382,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9248,17 +9392,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9273,12 +9417,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9291,60 +9435,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9358,7 +9506,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9368,33 +9516,37 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9559,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9417,7 +9569,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9427,40 +9579,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9474,7 +9630,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9484,17 +9640,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9509,12 +9665,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9683,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9537,7 +9693,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9547,40 +9703,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9594,7 +9754,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9604,17 +9764,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9629,12 +9789,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9807,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A00251D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9657,7 +9817,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9667,40 +9827,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9714,7 +9878,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9724,17 +9888,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9749,12 +9913,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9931,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9777,7 +9941,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9815,12 +9979,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9834,7 +9998,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9883,60 +10047,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9950,43 +10118,2551 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A66775D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AD105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1216,13 +1216,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1780,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1904,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2276,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2400,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2768,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2855,32 +2859,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2888,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2912,17 +2920,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2932,13 +2940,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3120,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3240,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3360,7 +3372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3480,7 +3492,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3600,7 +3612,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3654,7 +3666,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3852,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3960,7 +3972,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4080,7 +4092,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4200,7 +4212,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,7 +4332,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4364,13 +4376,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4456,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,7 +4580,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4618,7 +4634,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4704,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4812,7 +4828,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4866,7 +4882,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4948,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5068,7 +5084,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5192,7 +5208,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5246,7 +5262,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5279,32 +5295,36 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -5312,7 +5332,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5336,33 +5356,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5456,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5519,32 +5543,36 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5552,7 +5580,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5576,33 +5604,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5667,36 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5668,7 +5704,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5692,17 +5728,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5712,13 +5748,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5796,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5784,7 +5824,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5916,7 +5956,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6032,7 +6072,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6120,7 +6160,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6148,7 +6188,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6280,7 +6320,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6396,7 +6436,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6512,7 +6552,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6628,7 +6668,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6744,7 +6784,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6860,7 +6900,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6976,7 +7016,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7092,7 +7132,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7208,7 +7248,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7324,7 +7364,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7440,7 +7480,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7556,7 +7596,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7672,7 +7712,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7788,7 +7828,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7842,7 +7882,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7948,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8028,7 +8068,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8082,7 +8122,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8188,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8268,7 +8308,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8384,7 +8424,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8438,7 +8478,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8544,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8571,22 +8611,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8619,12 +8659,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8673,82 +8713,78 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8762,7 +8798,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8772,17 +8808,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8797,82 +8833,78 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8886,7 +8918,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8896,22 +8928,22 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8921,12 +8953,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8939,24 +8971,24 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8969,34 +9001,34 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9010,7 +9042,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9040,17 +9072,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9095,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9073,7 +9105,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9093,24 +9125,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9120,7 +9152,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9134,7 +9166,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9159,7 +9191,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9169,12 +9201,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9187,24 +9219,24 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9217,34 +9249,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9258,7 +9290,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9293,12 +9325,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9311,24 +9343,24 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9341,34 +9373,34 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9382,7 +9414,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9417,12 +9449,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9467,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9445,7 +9477,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9465,19 +9497,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9487,12 +9519,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9506,7 +9538,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9541,12 +9573,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9591,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9569,7 +9601,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9589,24 +9621,24 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -9616,7 +9648,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9630,7 +9662,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9665,12 +9697,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9715,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9693,7 +9725,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9713,34 +9745,34 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9754,7 +9786,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9789,12 +9821,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9839,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9817,7 +9849,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9837,12 +9869,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -9859,12 +9891,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9878,7 +9910,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9913,12 +9945,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9963,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9941,7 +9973,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9951,40 +9983,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9998,7 +10034,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10008,17 +10044,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10028,13 +10064,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10087,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A00251D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -10057,7 +10097,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -10077,34 +10117,34 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10118,7 +10158,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10153,12 +10193,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10211,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10181,7 +10221,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10219,12 +10259,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10238,7 +10278,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10263,7 +10303,7 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
@@ -10287,24 +10327,24 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A66775D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10317,34 +10357,34 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10358,7 +10398,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10383,22 +10423,22 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10411,64 +10451,60 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10482,7 +10518,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10492,37 +10528,33 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10567,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A66775D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10545,7 +10577,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10555,40 +10587,44 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10602,7 +10638,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10612,33 +10648,37 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10691,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10661,7 +10701,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10671,32 +10711,36 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10704,7 +10748,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10718,7 +10762,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10728,17 +10772,17 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10753,12 +10797,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10815,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10781,7 +10825,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10819,12 +10863,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10838,7 +10882,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10887,60 +10931,64 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10954,7 +11002,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10964,17 +11012,17 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10984,17 +11032,17 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11007,22 +11055,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -11055,12 +11103,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11074,7 +11122,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11123,22 +11171,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -11171,12 +11219,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11190,7 +11238,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11215,7 +11263,7 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -11225,12 +11273,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11243,22 +11291,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -11291,12 +11339,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11310,7 +11358,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11340,17 +11388,13 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11407,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11373,7 +11417,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11416,7 +11460,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11430,7 +11474,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11455,7 +11499,7 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
@@ -11465,12 +11509,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11527,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11493,7 +11537,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11536,7 +11580,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11550,7 +11594,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11585,12 +11629,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11647,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11613,7 +11657,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11651,12 +11695,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11670,7 +11714,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11705,12 +11749,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11723,22 +11767,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11776,7 +11820,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11790,7 +11834,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11825,12 +11869,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11843,22 +11887,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11891,12 +11935,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11910,7 +11954,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11945,12 +11989,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11963,7 +12007,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11973,7 +12017,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -12011,12 +12055,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12030,7 +12074,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -12065,12 +12109,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12083,22 +12127,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A00251D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -12131,12 +12175,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12150,7 +12194,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12180,13 +12224,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12247,7 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -12209,7 +12257,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12247,12 +12295,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12266,7 +12314,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12296,13 +12344,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12315,22 +12367,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -12363,12 +12415,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12382,7 +12434,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12412,17 +12464,13 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12435,22 +12483,22 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12483,7 +12531,7 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12502,7 +12550,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12532,17 +12580,13 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12599,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12565,7 +12609,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12603,12 +12647,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12622,45 +12666,521 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66775D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="X105" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z101" s="2" t="inlineStr">
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA101" s="2" t="inlineStr">
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC101" s="2" t="inlineStr">
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AD101" s="2" t="inlineStr">
+      <c r="AD105" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>

--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4928,17 +4928,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7404,17 +7404,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8264,17 +8264,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8384,17 +8384,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9728,17 +9728,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10464,17 +10464,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10712,17 +10712,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11452,17 +11452,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11505,12 +11505,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11629,24 +11629,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11743,32 +11743,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11776,7 +11780,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11800,17 +11804,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11820,17 +11824,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11863,32 +11867,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11896,7 +11904,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11920,17 +11928,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11940,17 +11948,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11983,32 +11991,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12016,7 +12028,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12040,17 +12052,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12060,12 +12072,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12103,32 +12115,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12136,7 +12152,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12160,17 +12176,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12180,12 +12196,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12223,32 +12239,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12256,7 +12276,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12280,17 +12300,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12300,17 +12320,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12396,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12425,12 +12445,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12496,7 +12516,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12540,12 +12560,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
@@ -12620,7 +12640,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12664,17 +12684,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12818,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13268,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13302,7 +13322,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13392,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13550,7 +13570,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13694,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -13744,7 +13764,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13798,7 +13818,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13888,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13912,17 +13932,17 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14144,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14168,17 +14188,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14322,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14520,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14678,7 +14698,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14888,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14988,7 +15008,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15112,7 +15132,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15156,17 +15176,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15380,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15404,17 +15424,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15500,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15658,7 +15678,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15748,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15772,17 +15792,17 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15926,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15996,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16154,7 +16174,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16224,7 +16244,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16268,17 +16288,17 @@
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16748,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16852,7 +16872,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16906,7 +16926,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17030,7 +17050,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17174,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17224,7 +17244,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17278,7 +17298,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17368,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17392,17 +17412,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17488,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17512,17 +17532,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17666,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17770,7 +17790,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17860,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17960,7 +17980,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18208,7 +18228,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18252,17 +18272,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18352,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18456,7 +18476,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18704,7 +18724,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -19130,7 +19150,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -19254,7 +19274,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19320,7 +19340,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19510,7 +19530,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19870,7 +19890,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -19940,7 +19960,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19984,17 +20004,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20084,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20188,7 +20208,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20232,17 +20252,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -20486,7 +20506,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20750,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20870,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20974,7 +20994,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21312,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21336,17 +21356,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21436,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21460,17 +21480,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21556,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21580,17 +21600,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21680,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21704,17 +21724,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21780,7 +21800,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21900,7 +21920,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22024,7 +22044,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22078,7 +22098,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22144,7 +22164,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22268,7 +22288,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22322,7 +22342,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22388,7 +22408,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22686,7 +22706,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22830,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22896,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23050,7 +23070,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23174,7 +23194,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -23240,7 +23260,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23666,7 +23686,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23699,32 +23719,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23732,7 +23756,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23756,17 +23780,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23776,17 +23800,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23852,7 +23876,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24055,32 +24079,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24088,7 +24116,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24112,17 +24140,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24132,17 +24160,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24175,32 +24203,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24208,7 +24240,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24232,17 +24264,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24252,17 +24284,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24328,7 +24360,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24415,32 +24447,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24448,7 +24484,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24472,17 +24508,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24492,17 +24528,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24535,32 +24571,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -24568,7 +24608,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24592,17 +24632,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24612,17 +24652,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24728,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24742,7 +24782,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24775,32 +24815,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24808,7 +24852,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24832,17 +24876,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24852,17 +24896,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -24895,12 +24939,12 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -24928,7 +24972,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -24936,10 +24980,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R199" s="2" t="inlineStr"/>
-      <c r="S199" s="2" t="inlineStr"/>
-      <c r="T199" s="2" t="inlineStr"/>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V199" s="2" t="inlineStr">
         <is>
           <t>19:45</t>
@@ -25015,12 +25075,12 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq41，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -25048,7 +25108,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25056,10 +25116,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R200" s="2" t="inlineStr"/>
-      <c r="S200" s="2" t="inlineStr"/>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
       <c r="T200" s="2" t="inlineStr"/>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V200" s="2" t="inlineStr">
         <is>
           <t>19:50</t>
@@ -25168,7 +25240,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25288,7 +25360,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25342,7 +25414,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25480,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25528,7 +25600,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25652,7 +25724,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25696,17 +25768,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26220,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26197,12 +26269,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -26272,7 +26344,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26326,7 +26398,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -26644,7 +26716,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26688,17 +26760,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26840,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26822,7 +26894,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27382,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -27624,7 +27696,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27668,17 +27740,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -27748,7 +27820,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27792,17 +27864,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -28232,7 +28304,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28286,7 +28358,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -28596,7 +28668,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28645,12 +28717,12 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28916,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28898,7 +28970,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -28968,7 +29040,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29012,17 +29084,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -29502,7 +29574,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -29572,7 +29644,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29616,17 +29688,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -29940,7 +30012,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30006,7 +30078,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -30316,7 +30388,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30382,7 +30454,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -32804,7 +32876,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32848,17 +32920,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -33544,7 +33616,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33593,12 +33665,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -33784,7 +33856,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33828,17 +33900,17 @@
       </c>
       <c r="AB271" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -33904,7 +33976,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -33958,7 +34030,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -34024,7 +34096,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34068,17 +34140,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -34268,7 +34340,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34322,7 +34394,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -34760,7 +34832,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34804,17 +34876,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35568,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35545,12 +35617,12 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -35620,7 +35692,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35664,17 +35736,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35940,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35912,17 +35984,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -36116,7 +36188,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36170,7 +36242,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -36484,7 +36556,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36538,7 +36610,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -36852,7 +36924,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36896,17 +36968,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -37197,24 +37269,24 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -37224,7 +37296,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37273,12 +37345,12 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -37464,7 +37536,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37518,7 +37590,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -37551,32 +37623,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37584,7 +37660,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37608,17 +37684,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37628,17 +37704,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37780,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37758,7 +37834,7 @@
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -37791,32 +37867,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -37824,7 +37904,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37848,17 +37928,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37868,17 +37948,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -37911,32 +37991,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -37944,7 +38028,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -37968,17 +38052,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -37988,17 +38072,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -38064,7 +38148,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38113,12 +38197,12 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -38184,7 +38268,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38228,17 +38312,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -38304,7 +38388,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38348,17 +38432,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-operations.xlsx
+++ b/data/export/2026-09-30-operations.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10096,17 +10096,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11700,17 +11700,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12249,24 +12249,24 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12363,32 +12363,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -12396,7 +12400,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12420,17 +12424,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12440,17 +12444,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12520,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12694,7 +12698,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12822,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13268,7 +13272,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13312,17 +13316,17 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13822,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14148,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14520,7 +14524,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14698,7 +14702,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14892,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14932,12 +14936,12 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15008,7 +15012,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15500,7 +15504,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15996,7 +16000,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16174,7 +16178,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16302,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16876,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16916,17 +16920,17 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17302,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17488,7 +17492,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17790,7 +17794,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17864,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17980,7 +17984,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18024,12 +18028,12 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18352,7 +18356,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18476,7 +18480,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18724,7 +18728,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -19890,7 +19894,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -20750,7 +20754,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20994,7 +20998,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21556,7 +21560,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21734,7 +21738,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21800,7 +21804,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21920,7 +21924,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21964,12 +21968,12 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
@@ -22044,7 +22048,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22088,17 +22092,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22168,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22342,7 +22346,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22408,7 +22412,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22896,7 +22900,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23070,7 +23074,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -23260,7 +23264,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23686,7 +23690,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24360,7 +24364,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24538,7 +24542,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24695,32 +24699,36 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -24728,7 +24736,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24752,17 +24760,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24772,17 +24780,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24860,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24944,7 +24952,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -24972,7 +24980,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25080,7 +25088,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq41，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq58，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -25108,7 +25116,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25207,32 +25215,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25240,7 +25252,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25264,17 +25276,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25284,12 +25296,12 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25414,7 +25426,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25480,7 +25492,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25600,7 +25612,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25724,7 +25736,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -26220,7 +26232,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26264,17 +26276,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -26398,7 +26410,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26728,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26894,7 +26906,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -27382,7 +27394,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -27696,7 +27708,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27820,7 +27832,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27874,7 +27886,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -28358,7 +28370,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -28668,7 +28680,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28712,17 +28724,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -28970,7 +28982,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -29040,7 +29052,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29574,7 +29586,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -29644,7 +29656,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29698,7 +29710,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -30078,7 +30090,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -30454,7 +30466,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -32876,7 +32888,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33616,7 +33628,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33660,17 +33672,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -33856,7 +33868,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -34030,7 +34042,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -34096,7 +34108,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34150,7 +34162,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34406,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -34832,7 +34844,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -35568,7 +35580,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35612,17 +35624,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -35692,7 +35704,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35940,7 +35952,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35994,7 +36006,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36254,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -36610,7 +36622,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -36924,7 +36936,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37296,7 +37308,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37340,17 +37352,17 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -37590,7 +37602,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -37660,7 +37672,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37834,7 +37846,7 @@
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -37904,7 +37916,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37958,7 +37970,7 @@
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38040,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38115,32 +38127,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38148,7 +38164,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38172,17 +38188,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38192,17 +38208,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -38268,7 +38284,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38388,7 +38404,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38442,7 +38458,7 @@
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
